--- a/results/02-2026/no-tariffs/beta/inputs-02-2026.xlsx
+++ b/results/02-2026/no-tariffs/beta/inputs-02-2026.xlsx
@@ -36563,13 +36563,13 @@
         <v>3334.7</v>
       </c>
       <c r="Q224" t="n">
-        <v>5094</v>
+        <v>4814</v>
       </c>
       <c r="R224" t="n">
         <v>2523.6</v>
       </c>
       <c r="S224" t="n">
-        <v>208.5</v>
+        <v>508.5</v>
       </c>
       <c r="T224" t="n">
         <v>98.524631049651</v>
@@ -36620,13 +36620,13 @@
         <v>346.267</v>
       </c>
       <c r="AJ224" t="n">
-        <v>-2820.984</v>
+        <v>-2787.384</v>
       </c>
       <c r="AK224" t="n">
         <v>-1458.912</v>
       </c>
       <c r="AL224" t="n">
-        <v>-174.643333333333</v>
+        <v>-184.643333333333</v>
       </c>
       <c r="AM224" t="n">
         <v>-69.5433333333333</v>
@@ -36721,7 +36721,7 @@
         <v>3374.4</v>
       </c>
       <c r="Q225" t="n">
-        <v>5210</v>
+        <v>4870</v>
       </c>
       <c r="R225" t="n">
         <v>2564.4</v>
@@ -36778,13 +36778,13 @@
         <v>372.882</v>
       </c>
       <c r="AJ225" t="n">
-        <v>-2892.528</v>
+        <v>-2818.128</v>
       </c>
       <c r="AK225" t="n">
         <v>-1479.144</v>
       </c>
       <c r="AL225" t="n">
-        <v>-175.923893795779</v>
+        <v>-185.923893795779</v>
       </c>
       <c r="AM225" t="n">
         <v>-69.0204400971171</v>
@@ -36879,7 +36879,7 @@
         <v>3406.55934738558</v>
       </c>
       <c r="Q226" t="n">
-        <v>5155.72638375752</v>
+        <v>4811.6327645887</v>
       </c>
       <c r="R226" t="n">
         <v>2587.09562716461</v>
@@ -36936,13 +36936,13 @@
         <v>384.007881017631</v>
       </c>
       <c r="AJ226" t="n">
-        <v>-2942.1211660509</v>
+        <v>-2843.22993175064</v>
       </c>
       <c r="AK226" t="n">
         <v>-1498.64947525975</v>
       </c>
       <c r="AL226" t="n">
-        <v>-176.784596300125</v>
+        <v>-186.784596300125</v>
       </c>
       <c r="AM226" t="n">
         <v>-68.7712908957292</v>
@@ -37037,7 +37037,7 @@
         <v>3439.07484965055</v>
       </c>
       <c r="Q227" t="n">
-        <v>5194.31169283682</v>
+        <v>4846.08610731864</v>
       </c>
       <c r="R227" t="n">
         <v>2620.25184393131</v>
@@ -37094,13 +37094,13 @@
         <v>389.669595040581</v>
       </c>
       <c r="AJ227" t="n">
-        <v>-2985.44256919132</v>
+        <v>-2865.16426462888</v>
       </c>
       <c r="AK227" t="n">
         <v>-1517.39969653151</v>
       </c>
       <c r="AL227" t="n">
-        <v>-177.357178947116</v>
+        <v>-187.357178947116</v>
       </c>
       <c r="AM227" t="n">
         <v>-68.6626879319807</v>
@@ -37195,7 +37195,7 @@
         <v>3472.3435009738</v>
       </c>
       <c r="Q228" t="n">
-        <v>5233.25674340286</v>
+        <v>4880.86048513566</v>
       </c>
       <c r="R228" t="n">
         <v>2650.12168418405</v>
@@ -37252,13 +37252,13 @@
         <v>398.812142047763</v>
       </c>
       <c r="AJ228" t="n">
-        <v>-3032.48779537421</v>
+        <v>-2890.56755696984</v>
       </c>
       <c r="AK228" t="n">
         <v>-1536.18256100372</v>
       </c>
       <c r="AL228" t="n">
-        <v>-177.099720923249</v>
+        <v>-187.099720923249</v>
       </c>
       <c r="AM228" t="n">
         <v>-68.6313761058242</v>
@@ -37353,7 +37353,7 @@
         <v>3502.99535439423</v>
       </c>
       <c r="Q229" t="n">
-        <v>5268.21068507222</v>
+        <v>4911.60468507222</v>
       </c>
       <c r="R229" t="n">
         <v>2678.17662038156</v>
@@ -37410,13 +37410,13 @@
         <v>409.328157071834</v>
       </c>
       <c r="AJ229" t="n">
-        <v>-3077.59637601267</v>
+        <v>-2913.77695273939</v>
       </c>
       <c r="AK229" t="n">
         <v>-1554.15264481363</v>
       </c>
       <c r="AL229" t="n">
-        <v>-176.976651531437</v>
+        <v>-186.976651531437</v>
       </c>
       <c r="AM229" t="n">
         <v>-68.4951103731197</v>
@@ -37511,7 +37511,7 @@
         <v>3535.00054689959</v>
       </c>
       <c r="Q230" t="n">
-        <v>5516.20086828743</v>
+        <v>5155.3456915902</v>
       </c>
       <c r="R230" t="n">
         <v>2703.7773350445</v>
@@ -37568,13 +37568,13 @@
         <v>412.861482268104</v>
       </c>
       <c r="AJ230" t="n">
-        <v>-3142.89107560299</v>
+        <v>-2956.91280662207</v>
       </c>
       <c r="AK230" t="n">
         <v>-1571.99262396792</v>
       </c>
       <c r="AL230" t="n">
-        <v>-176.003712838393</v>
+        <v>-186.003712838393</v>
       </c>
       <c r="AM230" t="n">
         <v>-68.3249650694424</v>
@@ -37669,7 +37669,7 @@
         <v>3566.92831397173</v>
       </c>
       <c r="Q231" t="n">
-        <v>5552.55013602524</v>
+        <v>5187.40597825737</v>
       </c>
       <c r="R231" t="n">
         <v>2729.4359962967</v>
@@ -37726,13 +37726,13 @@
         <v>415.112888561561</v>
       </c>
       <c r="AJ231" t="n">
-        <v>-3197.58045082168</v>
+        <v>-2989.18124290862</v>
       </c>
       <c r="AK231" t="n">
         <v>-1589.40434630063</v>
       </c>
       <c r="AL231" t="n">
-        <v>-174.402183649244</v>
+        <v>-184.402183649244</v>
       </c>
       <c r="AM231" t="n">
         <v>-68.2441226430012</v>
@@ -37827,7 +37827,7 @@
         <v>3597.72008416121</v>
       </c>
       <c r="Q232" t="n">
-        <v>5589.18100938792</v>
+        <v>5219.70769330657</v>
       </c>
       <c r="R232" t="n">
         <v>2756.14926865522</v>
@@ -37884,13 +37884,13 @@
         <v>418.04796048695</v>
       </c>
       <c r="AJ232" t="n">
-        <v>-3231.67011985099</v>
+        <v>-3017.38542461</v>
       </c>
       <c r="AK232" t="n">
         <v>-1606.49961843659</v>
       </c>
       <c r="AL232" t="n">
-        <v>-173.096688056935</v>
+        <v>-183.096688056935</v>
       </c>
       <c r="AM232" t="n">
         <v>-68.1728136075684</v>
@@ -37985,7 +37985,7 @@
         <v>3628.38316225891</v>
       </c>
       <c r="Q233" t="n">
-        <v>5625.32787415308</v>
+        <v>5251.48484615308</v>
       </c>
       <c r="R233" t="n">
         <v>2783.20121523231</v>
@@ -38042,13 +38042,13 @@
         <v>421.53848883758</v>
       </c>
       <c r="AJ233" t="n">
-        <v>-3260.95645658784</v>
+        <v>-3044.11924745293</v>
       </c>
       <c r="AK233" t="n">
         <v>-1622.85360448667</v>
       </c>
       <c r="AL233" t="n">
-        <v>-171.331862220655</v>
+        <v>-181.331862220655</v>
       </c>
       <c r="AM233" t="n">
         <v>-68.00376077917</v>
@@ -38200,13 +38200,13 @@
         <v>0</v>
       </c>
       <c r="AJ234" t="n">
-        <v>-2616.26201299912</v>
+        <v>-2442.23881997921</v>
       </c>
       <c r="AK234" t="n">
         <v>-1302.25891073748</v>
       </c>
       <c r="AL234" t="n">
-        <v>-155.691862220655</v>
+        <v>-165.691862220655</v>
       </c>
       <c r="AM234" t="n">
         <v>-61.8570941125033</v>
@@ -38358,13 +38358,13 @@
         <v>0</v>
       </c>
       <c r="AJ235" t="n">
-        <v>-1967.08363897972</v>
+        <v>-1836.38456277091</v>
       </c>
       <c r="AK235" t="n">
         <v>-978.05172718766</v>
       </c>
       <c r="AL235" t="n">
-        <v>-140.035195553988</v>
+        <v>-150.035195553988</v>
       </c>
       <c r="AM235" t="n">
         <v>-55.7570941125033</v>
@@ -38516,7 +38516,7 @@
         <v>0</v>
       </c>
       <c r="AJ236" t="n">
-        <v>-1653.08823437555</v>
+        <v>-1543.53293366277</v>
       </c>
       <c r="AK236" t="n">
         <v>-819.044426136617</v>
@@ -38674,7 +38674,7 @@
         <v>0</v>
       </c>
       <c r="AJ237" t="n">
-        <v>-1336.99559327122</v>
+        <v>-1248.83665255843</v>
       </c>
       <c r="AK237" t="n">
         <v>-658.353828913723</v>
@@ -38832,7 +38832,7 @@
         <v>0</v>
       </c>
       <c r="AJ238" t="n">
-        <v>-1006.02354117397</v>
+        <v>-939.515911063022</v>
       </c>
       <c r="AK238" t="n">
         <v>-496.127188811054</v>
@@ -38990,7 +38990,7 @@
         <v>0</v>
       </c>
       <c r="AJ239" t="n">
-        <v>-672.87053301246</v>
+        <v>-628.271552367579</v>
       </c>
       <c r="AK239" t="n">
         <v>-332.361029033251</v>
@@ -39148,7 +39148,7 @@
         <v>0</v>
       </c>
       <c r="AJ240" t="n">
-        <v>-337.519672449185</v>
+        <v>-315.089090769185</v>
       </c>
       <c r="AK240" t="n">
         <v>-166.992072913939</v>
